--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="history" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3610"/>
+  <dimension ref="A1:E3612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -97843,17 +97844,17 @@
           <t>Loteria Nacional- Gana Más</t>
         </is>
       </c>
-      <c r="C3609" t="inlineStr">
+      <c r="C3609" s="1" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D3609" t="inlineStr">
+      <c r="D3609" s="1" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="E3609" t="inlineStr">
+      <c r="E3609" s="1" t="inlineStr">
         <is>
           <t>41</t>
         </is>
@@ -97870,17 +97871,71 @@
           <t>Loteria Nacional- Noche</t>
         </is>
       </c>
-      <c r="C3610" t="inlineStr">
+      <c r="C3610" s="1" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D3610" t="inlineStr">
+      <c r="D3610" s="1" t="inlineStr">
         <is>
           <t>99</t>
         </is>
       </c>
-      <c r="E3610" t="inlineStr">
+      <c r="E3610" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3611" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3611" s="1" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3611" s="1" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3612" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3612" s="1" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3612" s="1" t="inlineStr">
         <is>
           <t>21</t>
         </is>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3593"/>
+  <dimension ref="A1:E3594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97430,6 +97430,33 @@
         </is>
       </c>
     </row>
+    <row r="3594">
+      <c r="A3594" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3594" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3594" s="1" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D3594" s="1" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E3594" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3594"/>
+  <dimension ref="A1:E3595"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97457,6 +97457,33 @@
         </is>
       </c>
     </row>
+    <row r="3595">
+      <c r="A3595" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B3595" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3595" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3595" s="1" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3595" s="1" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3595"/>
+  <dimension ref="A1:E3596"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97484,6 +97484,33 @@
         </is>
       </c>
     </row>
+    <row r="3596">
+      <c r="A3596" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B3596" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3596" s="1" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D3596" s="1" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3596" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3596"/>
+  <dimension ref="A1:E3597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97511,6 +97511,33 @@
         </is>
       </c>
     </row>
+    <row r="3597">
+      <c r="A3597" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B3597" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3597" s="1" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D3597" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3597" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3597"/>
+  <dimension ref="A1:E3598"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97538,6 +97538,33 @@
         </is>
       </c>
     </row>
+    <row r="3598">
+      <c r="A3598" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B3598" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3598" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3598" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3598" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3598"/>
+  <dimension ref="A1:E3599"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97565,6 +97565,33 @@
         </is>
       </c>
     </row>
+    <row r="3599">
+      <c r="A3599" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B3599" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3599" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D3599" s="1" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E3599" s="1" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3599"/>
+  <dimension ref="A1:E3600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97592,6 +97592,33 @@
         </is>
       </c>
     </row>
+    <row r="3600">
+      <c r="A3600" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B3600" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3600" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D3600" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3600" s="1" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3600"/>
+  <dimension ref="A1:E3601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97619,6 +97619,33 @@
         </is>
       </c>
     </row>
+    <row r="3601">
+      <c r="A3601" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B3601" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3601" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3601" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3601" s="1" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3601"/>
+  <dimension ref="A1:E3602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97646,6 +97646,33 @@
         </is>
       </c>
     </row>
+    <row r="3602">
+      <c r="A3602" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3602" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3602" s="1" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3602" s="1" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3602" s="1" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3602"/>
+  <dimension ref="A1:E3603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97673,6 +97673,33 @@
         </is>
       </c>
     </row>
+    <row r="3603">
+      <c r="A3603" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="B3603" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3603" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3603" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3603" s="1" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3603"/>
+  <dimension ref="A1:E3604"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97700,6 +97700,33 @@
         </is>
       </c>
     </row>
+    <row r="3604">
+      <c r="A3604" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B3604" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3604" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3604" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E3604" s="1" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3604"/>
+  <dimension ref="A1:E3605"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97727,6 +97727,33 @@
         </is>
       </c>
     </row>
+    <row r="3605">
+      <c r="A3605" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B3605" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3605" s="1" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D3605" s="1" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E3605" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3605"/>
+  <dimension ref="A1:E3606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97754,6 +97754,33 @@
         </is>
       </c>
     </row>
+    <row r="3606">
+      <c r="A3606" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B3606" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3606" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D3606" s="1" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3606" s="1" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3606"/>
+  <dimension ref="A1:E3607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97781,6 +97781,33 @@
         </is>
       </c>
     </row>
+    <row r="3607">
+      <c r="A3607" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B3607" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3607" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3607" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3607" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3607"/>
+  <dimension ref="A1:E3608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97808,6 +97808,33 @@
         </is>
       </c>
     </row>
+    <row r="3608">
+      <c r="A3608" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B3608" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3608" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3608" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3608" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3608"/>
+  <dimension ref="A1:E3609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97835,6 +97835,33 @@
         </is>
       </c>
     </row>
+    <row r="3609">
+      <c r="A3609" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B3609" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3609" s="1" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="D3609" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E3609" s="1" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3609"/>
+  <dimension ref="A1:E3610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97862,6 +97862,33 @@
         </is>
       </c>
     </row>
+    <row r="3610">
+      <c r="A3610" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B3610" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3610" s="1" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3610" s="1" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E3610" s="1" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3610"/>
+  <dimension ref="A1:E3611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97889,6 +97889,33 @@
         </is>
       </c>
     </row>
+    <row r="3611">
+      <c r="A3611" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="B3611" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3611" s="1" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D3611" s="1" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3611" s="1" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3611"/>
+  <dimension ref="A1:E3612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97916,6 +97916,33 @@
         </is>
       </c>
     </row>
+    <row r="3612">
+      <c r="A3612" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B3612" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3612" s="1" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3612" s="1" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="E3612" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3612"/>
+  <dimension ref="A1:E3613"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97943,6 +97943,33 @@
         </is>
       </c>
     </row>
+    <row r="3613">
+      <c r="A3613" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="B3613" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3613" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3613" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E3613" s="1" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3613"/>
+  <dimension ref="A1:E3614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97970,6 +97970,33 @@
         </is>
       </c>
     </row>
+    <row r="3614">
+      <c r="A3614" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3614" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3614" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3614" s="1" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E3614" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3614"/>
+  <dimension ref="A1:E3615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -97997,6 +97997,33 @@
         </is>
       </c>
     </row>
+    <row r="3615">
+      <c r="A3615" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B3615" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3615" s="1" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3615" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3615" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3615"/>
+  <dimension ref="A1:E3616"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98024,6 +98024,33 @@
         </is>
       </c>
     </row>
+    <row r="3616">
+      <c r="A3616" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B3616" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3616" s="1" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3616" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3616" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3616"/>
+  <dimension ref="A1:E3617"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98051,6 +98051,33 @@
         </is>
       </c>
     </row>
+    <row r="3617">
+      <c r="A3617" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="B3617" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3617" s="1" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3617" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3617" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3617"/>
+  <dimension ref="A1:E3618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98078,6 +98078,33 @@
         </is>
       </c>
     </row>
+    <row r="3618">
+      <c r="A3618" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B3618" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3618" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3618" s="1" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3618" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3618"/>
+  <dimension ref="A1:E3619"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98105,6 +98105,33 @@
         </is>
       </c>
     </row>
+    <row r="3619">
+      <c r="A3619" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="B3619" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3619" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3619" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E3619" s="1" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3619"/>
+  <dimension ref="A1:E3620"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98132,6 +98132,33 @@
         </is>
       </c>
     </row>
+    <row r="3620">
+      <c r="A3620" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B3620" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3620" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3620" s="1" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3620" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3620"/>
+  <dimension ref="A1:E3621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98159,6 +98159,33 @@
         </is>
       </c>
     </row>
+    <row r="3621">
+      <c r="A3621" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B3621" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3621" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3621" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3621" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3621"/>
+  <dimension ref="A1:E3622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98186,6 +98186,33 @@
         </is>
       </c>
     </row>
+    <row r="3622">
+      <c r="A3622" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B3622" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3622" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3622" s="1" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E3622" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3622"/>
+  <dimension ref="A1:E3623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98213,6 +98213,33 @@
         </is>
       </c>
     </row>
+    <row r="3623">
+      <c r="A3623" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="B3623" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3623" s="1" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3623" s="1" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3623" s="1" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3623"/>
+  <dimension ref="A1:E3624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98240,6 +98240,33 @@
         </is>
       </c>
     </row>
+    <row r="3624">
+      <c r="A3624" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B3624" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3624" s="1" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D3624" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3624" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3624"/>
+  <dimension ref="A1:E3625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98267,6 +98267,33 @@
         </is>
       </c>
     </row>
+    <row r="3625">
+      <c r="A3625" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="B3625" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3625" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3625" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3625" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3625"/>
+  <dimension ref="A1:E3626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98294,6 +98294,33 @@
         </is>
       </c>
     </row>
+    <row r="3626">
+      <c r="A3626" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B3626" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3626" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3626" s="1" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E3626" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3626"/>
+  <dimension ref="A1:E3627"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98321,6 +98321,33 @@
         </is>
       </c>
     </row>
+    <row r="3627">
+      <c r="A3627" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B3627" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3627" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D3627" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E3627" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3627"/>
+  <dimension ref="A1:E3628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98348,6 +98348,33 @@
         </is>
       </c>
     </row>
+    <row r="3628">
+      <c r="A3628" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B3628" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3628" s="1" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3628" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3628" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3628"/>
+  <dimension ref="A1:E3629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98375,6 +98375,33 @@
         </is>
       </c>
     </row>
+    <row r="3629">
+      <c r="A3629" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="B3629" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3629" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3629" s="1" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E3629" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3629"/>
+  <dimension ref="A1:E3630"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98402,6 +98402,33 @@
         </is>
       </c>
     </row>
+    <row r="3630">
+      <c r="A3630" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3630" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3630" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D3630" s="1" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E3630" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3630"/>
+  <dimension ref="A1:E3631"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98429,6 +98429,33 @@
         </is>
       </c>
     </row>
+    <row r="3631">
+      <c r="A3631" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B3631" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3631" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D3631" s="1" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="E3631" s="1" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3631"/>
+  <dimension ref="A1:E3632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98456,6 +98456,33 @@
         </is>
       </c>
     </row>
+    <row r="3632">
+      <c r="A3632" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B3632" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3632" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3632" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3632" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3632"/>
+  <dimension ref="A1:E3633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98483,6 +98483,33 @@
         </is>
       </c>
     </row>
+    <row r="3633">
+      <c r="A3633" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B3633" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3633" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3633" s="1" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E3633" s="1" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3633"/>
+  <dimension ref="A1:E3634"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98510,6 +98510,33 @@
         </is>
       </c>
     </row>
+    <row r="3634">
+      <c r="A3634" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B3634" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3634" s="1" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D3634" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E3634" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3634"/>
+  <dimension ref="A1:E3635"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98537,6 +98537,33 @@
         </is>
       </c>
     </row>
+    <row r="3635">
+      <c r="A3635" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B3635" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3635" s="1" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D3635" s="1" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E3635" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3635"/>
+  <dimension ref="A1:E3636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98564,6 +98564,33 @@
         </is>
       </c>
     </row>
+    <row r="3636">
+      <c r="A3636" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B3636" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3636" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D3636" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E3636" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3636"/>
+  <dimension ref="A1:E3637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98591,6 +98591,33 @@
         </is>
       </c>
     </row>
+    <row r="3637">
+      <c r="A3637" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B3637" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3637" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3637" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E3637" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3637"/>
+  <dimension ref="A1:E3638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98618,6 +98618,33 @@
         </is>
       </c>
     </row>
+    <row r="3638">
+      <c r="A3638" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B3638" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3638" s="1" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3638" s="1" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="E3638" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3638"/>
+  <dimension ref="A1:E3639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98645,6 +98645,33 @@
         </is>
       </c>
     </row>
+    <row r="3639">
+      <c r="A3639" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B3639" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3639" s="1" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D3639" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3639" s="1" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3639"/>
+  <dimension ref="A1:E3640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98672,6 +98672,33 @@
         </is>
       </c>
     </row>
+    <row r="3640">
+      <c r="A3640" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B3640" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3640" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3640" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E3640" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3640"/>
+  <dimension ref="A1:E3641"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98699,6 +98699,33 @@
         </is>
       </c>
     </row>
+    <row r="3641">
+      <c r="A3641" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B3641" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3641" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D3641" s="1" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3641" s="1" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3641"/>
+  <dimension ref="A1:E3642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98726,6 +98726,33 @@
         </is>
       </c>
     </row>
+    <row r="3642">
+      <c r="A3642" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B3642" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3642" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3642" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E3642" s="1" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3642"/>
+  <dimension ref="A1:E3643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98753,6 +98753,33 @@
         </is>
       </c>
     </row>
+    <row r="3643">
+      <c r="A3643" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B3643" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3643" s="1" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D3643" s="1" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3643" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3643"/>
+  <dimension ref="A1:E3644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98780,6 +98780,33 @@
         </is>
       </c>
     </row>
+    <row r="3644">
+      <c r="A3644" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3644" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3644" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D3644" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3644" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3644"/>
+  <dimension ref="A1:E3645"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98807,6 +98807,33 @@
         </is>
       </c>
     </row>
+    <row r="3645">
+      <c r="A3645" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B3645" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3645" s="1" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3645" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E3645" s="1" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3645"/>
+  <dimension ref="A1:E3646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98834,6 +98834,33 @@
         </is>
       </c>
     </row>
+    <row r="3646">
+      <c r="A3646" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3646" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3646" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D3646" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3646" s="1" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3646"/>
+  <dimension ref="A1:E3647"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98861,6 +98861,33 @@
         </is>
       </c>
     </row>
+    <row r="3647">
+      <c r="A3647" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B3647" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3647" s="1" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D3647" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3647" s="1" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3647"/>
+  <dimension ref="A1:E3648"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98888,6 +98888,33 @@
         </is>
       </c>
     </row>
+    <row r="3648">
+      <c r="A3648" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3648" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3648" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D3648" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E3648" s="1" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3648"/>
+  <dimension ref="A1:E3649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98915,6 +98915,33 @@
         </is>
       </c>
     </row>
+    <row r="3649">
+      <c r="A3649" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B3649" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3649" s="1" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="D3649" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3649" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3649"/>
+  <dimension ref="A1:E3650"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98942,6 +98942,33 @@
         </is>
       </c>
     </row>
+    <row r="3650">
+      <c r="A3650" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3650" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3650" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D3650" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E3650" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3650"/>
+  <dimension ref="A1:E3651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98969,6 +98969,33 @@
         </is>
       </c>
     </row>
+    <row r="3651">
+      <c r="A3651" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3651" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3651" s="1" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3651" s="1" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3651" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3651"/>
+  <dimension ref="A1:E3652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -98996,6 +98996,33 @@
         </is>
       </c>
     </row>
+    <row r="3652">
+      <c r="A3652" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B3652" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3652" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3652" s="1" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="E3652" s="1" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3652"/>
+  <dimension ref="A1:E3653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99023,6 +99023,33 @@
         </is>
       </c>
     </row>
+    <row r="3653">
+      <c r="A3653" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B3653" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3653" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3653" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3653" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3653"/>
+  <dimension ref="A1:E3654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99050,6 +99050,33 @@
         </is>
       </c>
     </row>
+    <row r="3654">
+      <c r="A3654" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B3654" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3654" s="1" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="D3654" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E3654" s="1" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3654"/>
+  <dimension ref="A1:E3655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99077,6 +99077,33 @@
         </is>
       </c>
     </row>
+    <row r="3655">
+      <c r="A3655" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B3655" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3655" s="1" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="D3655" s="1" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E3655" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3655"/>
+  <dimension ref="A1:E3656"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99104,6 +99104,33 @@
         </is>
       </c>
     </row>
+    <row r="3656">
+      <c r="A3656" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B3656" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3656" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3656" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3656" s="1" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3656"/>
+  <dimension ref="A1:E3657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99131,6 +99131,33 @@
         </is>
       </c>
     </row>
+    <row r="3657">
+      <c r="A3657" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B3657" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3657" s="1" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D3657" s="1" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3657" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3657"/>
+  <dimension ref="A1:E3658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99158,6 +99158,33 @@
         </is>
       </c>
     </row>
+    <row r="3658">
+      <c r="A3658" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B3658" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3658" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D3658" s="1" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E3658" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3658"/>
+  <dimension ref="A1:E3659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99185,6 +99185,33 @@
         </is>
       </c>
     </row>
+    <row r="3659">
+      <c r="A3659" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B3659" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3659" s="1" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3659" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E3659" s="1" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3659"/>
+  <dimension ref="A1:E3660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99212,6 +99212,33 @@
         </is>
       </c>
     </row>
+    <row r="3660">
+      <c r="A3660" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B3660" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3660" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3660" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3660" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3660"/>
+  <dimension ref="A1:E3661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99239,6 +99239,33 @@
         </is>
       </c>
     </row>
+    <row r="3661">
+      <c r="A3661" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B3661" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3661" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3661" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E3661" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3661"/>
+  <dimension ref="A1:E3662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99266,6 +99266,33 @@
         </is>
       </c>
     </row>
+    <row r="3662">
+      <c r="A3662" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B3662" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3662" s="1" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3662" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3662" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3662"/>
+  <dimension ref="A1:E3663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99293,6 +99293,33 @@
         </is>
       </c>
     </row>
+    <row r="3663">
+      <c r="A3663" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B3663" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3663" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D3663" s="1" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="E3663" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3663"/>
+  <dimension ref="A1:E3664"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99320,6 +99320,33 @@
         </is>
       </c>
     </row>
+    <row r="3664">
+      <c r="A3664" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B3664" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3664" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3664" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3664" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3664"/>
+  <dimension ref="A1:E3665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99347,6 +99347,33 @@
         </is>
       </c>
     </row>
+    <row r="3665">
+      <c r="A3665" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B3665" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3665" s="1" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D3665" s="1" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3665" s="1" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3665"/>
+  <dimension ref="A1:E3666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99374,6 +99374,33 @@
         </is>
       </c>
     </row>
+    <row r="3666">
+      <c r="A3666" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B3666" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3666" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D3666" s="1" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="E3666" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3666"/>
+  <dimension ref="A1:E3667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99401,6 +99401,33 @@
         </is>
       </c>
     </row>
+    <row r="3667">
+      <c r="A3667" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B3667" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3667" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D3667" s="1" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E3667" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3667"/>
+  <dimension ref="A1:E3668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99428,6 +99428,33 @@
         </is>
       </c>
     </row>
+    <row r="3668">
+      <c r="A3668" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3668" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3668" s="1" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D3668" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3668" s="1" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3668"/>
+  <dimension ref="A1:E3669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99455,6 +99455,33 @@
         </is>
       </c>
     </row>
+    <row r="3669">
+      <c r="A3669" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B3669" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3669" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D3669" s="1" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3669" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3669"/>
+  <dimension ref="A1:E3670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99482,6 +99482,33 @@
         </is>
       </c>
     </row>
+    <row r="3670">
+      <c r="A3670" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3670" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3670" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D3670" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E3670" s="1" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3670"/>
+  <dimension ref="A1:E3671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99509,6 +99509,33 @@
         </is>
       </c>
     </row>
+    <row r="3671">
+      <c r="A3671" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B3671" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3671" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3671" s="1" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E3671" s="1" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3671"/>
+  <dimension ref="A1:E3672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99536,6 +99536,33 @@
         </is>
       </c>
     </row>
+    <row r="3672">
+      <c r="A3672" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B3672" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3672" s="1" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D3672" s="1" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="E3672" s="1" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3672"/>
+  <dimension ref="A1:E3673"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99563,6 +99563,33 @@
         </is>
       </c>
     </row>
+    <row r="3673">
+      <c r="A3673" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B3673" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3673" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D3673" s="1" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E3673" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3673"/>
+  <dimension ref="A1:E3674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99590,6 +99590,33 @@
         </is>
       </c>
     </row>
+    <row r="3674">
+      <c r="A3674" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3674" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3674" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3674" s="1" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3674" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3674"/>
+  <dimension ref="A1:E3675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99617,6 +99617,33 @@
         </is>
       </c>
     </row>
+    <row r="3675">
+      <c r="A3675" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B3675" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3675" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3675" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3675" s="1" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3675"/>
+  <dimension ref="A1:E3676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99644,6 +99644,33 @@
         </is>
       </c>
     </row>
+    <row r="3676">
+      <c r="A3676" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B3676" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3676" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3676" s="1" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E3676" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3676"/>
+  <dimension ref="A1:E3677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99671,6 +99671,33 @@
         </is>
       </c>
     </row>
+    <row r="3677">
+      <c r="A3677" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B3677" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3677" s="1" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D3677" s="1" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E3677" s="1" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3677"/>
+  <dimension ref="A1:E3678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99698,6 +99698,33 @@
         </is>
       </c>
     </row>
+    <row r="3678">
+      <c r="A3678" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B3678" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3678" s="1" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D3678" s="1" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E3678" s="1" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3678"/>
+  <dimension ref="A1:E3679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99725,6 +99725,33 @@
         </is>
       </c>
     </row>
+    <row r="3679">
+      <c r="A3679" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B3679" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3679" s="1" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D3679" s="1" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E3679" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3679"/>
+  <dimension ref="A1:E3680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99752,6 +99752,33 @@
         </is>
       </c>
     </row>
+    <row r="3680">
+      <c r="A3680" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3680" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3680" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D3680" s="1" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E3680" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3680"/>
+  <dimension ref="A1:E3681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99779,6 +99779,33 @@
         </is>
       </c>
     </row>
+    <row r="3681">
+      <c r="A3681" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B3681" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3681" s="1" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="D3681" s="1" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3681" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3681"/>
+  <dimension ref="A1:E3682"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99806,6 +99806,33 @@
         </is>
       </c>
     </row>
+    <row r="3682">
+      <c r="A3682" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3682" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3682" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D3682" s="1" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E3682" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3682"/>
+  <dimension ref="A1:E3683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99833,6 +99833,33 @@
         </is>
       </c>
     </row>
+    <row r="3683">
+      <c r="A3683" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B3683" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3683" s="1" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D3683" s="1" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E3683" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3683"/>
+  <dimension ref="A1:E3684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99860,6 +99860,33 @@
         </is>
       </c>
     </row>
+    <row r="3684">
+      <c r="A3684" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3684" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3684" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D3684" s="1" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E3684" s="1" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3684"/>
+  <dimension ref="A1:E3685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99887,6 +99887,33 @@
         </is>
       </c>
     </row>
+    <row r="3685">
+      <c r="A3685" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B3685" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3685" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D3685" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3685" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3685"/>
+  <dimension ref="A1:E3686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99914,6 +99914,33 @@
         </is>
       </c>
     </row>
+    <row r="3686">
+      <c r="A3686" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3686" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3686" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D3686" s="1" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E3686" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3686"/>
+  <dimension ref="A1:E3687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99941,6 +99941,33 @@
         </is>
       </c>
     </row>
+    <row r="3687">
+      <c r="A3687" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B3687" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3687" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3687" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E3687" s="1" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3687"/>
+  <dimension ref="A1:E3688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99968,6 +99968,33 @@
         </is>
       </c>
     </row>
+    <row r="3688">
+      <c r="A3688" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B3688" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3688" s="1" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D3688" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E3688" s="1" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3688"/>
+  <dimension ref="A1:E3689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -99995,6 +99995,33 @@
         </is>
       </c>
     </row>
+    <row r="3689">
+      <c r="A3689" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B3689" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3689" s="1" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D3689" s="1" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3689" s="1" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3689"/>
+  <dimension ref="A1:E3690"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100022,6 +100022,33 @@
         </is>
       </c>
     </row>
+    <row r="3690">
+      <c r="A3690" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B3690" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3690" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D3690" s="1" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3690" s="1" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3690"/>
+  <dimension ref="A1:E3691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100049,6 +100049,33 @@
         </is>
       </c>
     </row>
+    <row r="3691">
+      <c r="A3691" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B3691" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3691" s="1" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D3691" s="1" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E3691" s="1" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3691"/>
+  <dimension ref="A1:E3692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100076,6 +100076,33 @@
         </is>
       </c>
     </row>
+    <row r="3692">
+      <c r="A3692" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B3692" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3692" s="1" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D3692" s="1" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E3692" s="1" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3692"/>
+  <dimension ref="A1:E3693"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100103,6 +100103,33 @@
         </is>
       </c>
     </row>
+    <row r="3693">
+      <c r="A3693" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B3693" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3693" s="1" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D3693" s="1" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E3693" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3693"/>
+  <dimension ref="A1:E3694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100130,6 +100130,33 @@
         </is>
       </c>
     </row>
+    <row r="3694">
+      <c r="A3694" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3694" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3694" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3694" s="1" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E3694" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3694"/>
+  <dimension ref="A1:E3695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100157,6 +100157,33 @@
         </is>
       </c>
     </row>
+    <row r="3695">
+      <c r="A3695" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B3695" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3695" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D3695" s="1" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E3695" s="1" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3695"/>
+  <dimension ref="A1:E3696"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100184,6 +100184,33 @@
         </is>
       </c>
     </row>
+    <row r="3696">
+      <c r="A3696" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3696" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3696" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D3696" s="1" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E3696" s="1" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3696"/>
+  <dimension ref="A1:E3697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100211,6 +100211,33 @@
         </is>
       </c>
     </row>
+    <row r="3697">
+      <c r="A3697" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B3697" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3697" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D3697" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E3697" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3697"/>
+  <dimension ref="A1:E3698"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100238,6 +100238,33 @@
         </is>
       </c>
     </row>
+    <row r="3698">
+      <c r="A3698" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3698" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Gana Más</t>
+        </is>
+      </c>
+      <c r="C3698" s="1" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D3698" s="1" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E3698" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/la_nacional_history.xlsx
+++ b/data/la_nacional_history.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3698"/>
+  <dimension ref="A1:E3699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18.28515625" customWidth="1" min="1" max="1"/>
@@ -100265,6 +100265,33 @@
         </is>
       </c>
     </row>
+    <row r="3699">
+      <c r="A3699" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B3699" t="inlineStr">
+        <is>
+          <t>Loteria Nacional- Noche</t>
+        </is>
+      </c>
+      <c r="C3699" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D3699" s="1" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="E3699" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
